--- a/submission/knowledge/A11-武汉多语翻译官/武汉多语翻译官QA导入表.xlsx
+++ b/submission/knowledge/A11-武汉多语翻译官/武汉多语翻译官QA导入表.xlsx
@@ -367,6 +367,584 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wuhan University cherries?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campus booking, free, capped. Not East Lake's paid garden. Check this year's notice.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How to pay the metro?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QR via Metro app / Alipay / WeChat / UnionPay, or a machine ticket. Same app in and out.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Which railway station?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wuhan, Hankou, and Wuchang are different. Read the ticket.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stations</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exact ticket price?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will not invent it. Official WeChat or window today.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tourism complaint?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12345. 12301 is cancelled. Emergency 120.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">complain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Are museums closed on Monday?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Often yes, except national holidays. The 1911 museum south and north areas differ. Check today.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monday</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can a wheelchair go up Yellow Crane Tower?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Many stairs. Do not promise the top. Some museums have accessible routes.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wheelchair</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can I bring a dog?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most heritage parks restrict pets. Check the park WeChat.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sesame allergy?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tell the shop: no sesame paste. Consider other breakfast dishes.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allergy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hubu Lane vs Jiqing Street?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Different streets: Wuchang vs Hankou.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lane</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you say 东湖?</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">East Lake / East Lake Scenic Area. Tingtao, Moshan and Luoyan are different gardens.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖北省博物馆 in English?</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hubei Provincial Museum. Free with official reservation; often closed Mondays except national holidays.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥革命博物院?</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1911 Revolution Museum / Wuchang Uprising Memorial. Personal visits usually need no online booking; south and north areas have different closed days.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川阁?</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qingchuan Pavilion / Yu the Great museum in Hanyang. Daytime is often free per the official notice; night tours are separate.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow Crane Tower booking?</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal notices in 2024 said no real-name reservation for the day park. Buy via Huanghelou Park WeChat or the window. I will not invent today’s price.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Night show same ticket?</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. Night Huanghelou is a separate performance ticket. Riverside lighting is usually free.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is 过早?</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wuhan breakfast. Reganmian is dry noodles with sesame paste, not soup. Doupi is stuffed rice-and-egg crepe.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">food</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hubu Lane ticket?</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. It is a snack street in Wuchang, not a gated park. Jiqing Street is in Hankou—different place.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">food</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airport station name?</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tianhe Airport Station on Metro Line 2. Last trains: follow station screens, often around 23:00 at terminals.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three railway stations?</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wuhan Railway Station (east), Hankou Station, Wuchang Station. Read the ticket. They are not the same.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferry 1.5 yuan?</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provincial media in 2026 cited about 1.5 yuan on the Wuzhong line, roughly 06:30–20:00. Not the night cruise.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ferry</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provincial museum ticket release time?</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports have mentioned 17:18 and also midnight. Follow the page you opened. Book 1–5 days ahead as the site says.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">museum</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">East Lake vs university?</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wuhan University is a campus, free capped booking. East Lake cherry garden is often a paid garden in Moshan. Not one ticket.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wheelchair at the 1911 museum?</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The notice mentions accessible routes with a companion. Do not promise Yellow Crane Tower summit.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">access</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Police number?</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110. Ambulance 120. City hotline 027-12345. 12301 is cancelled.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lost passport?</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Police 110, then embassy/consulate guidance. I do not replace documents.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where to complain?</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">027-12345 or jbts.mct.gov.cn. No private WeChat.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">complaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opera photos?</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow the theatre. Usually no flash. Hanju and Chuju are different operas.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etiquette</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your WeChat?</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. Official WeChat accounts of the parks only.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Translate a medical prescription?</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will not give a legal or medical conclusion. Emergency: call 120.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No chili please?</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「不要辣椒。」 For sesame allergy: say you cannot eat sesame paste.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where is the toilet?</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「洗手间在哪里？」 Follow park signs.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Which town to stay?</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">That is the transport-and-hotel steward in Chinese. Wuchang for the tower, Hankou for shopping, Hanyang for Guqin Terrace.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One day three towns?</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The itinerary planner will say no. Stay in one town as the main day.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planner</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>